--- a/data/monthly_safety_reports.xlsx
+++ b/data/monthly_safety_reports.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -64,7 +64,25 @@
     <t>Updated_At</t>
   </si>
   <si>
-    <t>5a337c4b4d5140c48384f1e4d60bd1ac</t>
+    <t>SHE_Staff</t>
+  </si>
+  <si>
+    <t>SHE_Staff_Comment</t>
+  </si>
+  <si>
+    <t>5ccca35e88224b449a254cc79730a356</t>
+  </si>
+  <si>
+    <t>5460b636e23b46aab9fc27f9866a764c</t>
+  </si>
+  <si>
+    <t>53de2581eef04cacbf64a6859d84dcbe</t>
+  </si>
+  <si>
+    <t>517955eaf98640af92085cba34d4f8f8</t>
+  </si>
+  <si>
+    <t>73a22ce99bd7486798c6aec72250b8d5</t>
   </si>
   <si>
     <t>MSR-2025-12-001</t>
@@ -73,42 +91,121 @@
     <t>2025-05</t>
   </si>
   <si>
+    <t>2024-11</t>
+  </si>
+  <si>
+    <t>2025-01</t>
+  </si>
+  <si>
     <t>Humphrey Lungu</t>
   </si>
   <si>
+    <t>Peter Sibale</t>
+  </si>
+  <si>
     <t xml:space="preserve">Safety Officer </t>
   </si>
   <si>
+    <t>Area Manager</t>
+  </si>
+  <si>
+    <t>{"Human Resources": {"permanent": 0, "seasonal": 0, "casual": 0}, "General Agriculture": {"permanent": 1, "seasonal": 4, "casual": 0}, "Accounts Department": {"permanent": 0, "seasonal": 0, "casual": 0}}</t>
+  </si>
+  <si>
+    <t>{"Human Resources": {"permanent": 1, "seasonal": 0, "casual": 0}, "General Agriculture": {"permanent": 0, "seasonal": 3, "casual": 1}, "Accounts Department": {"permanent": 0, "seasonal": 0, "casual": 0}}</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t xml:space="preserve">•	All employees of both Chawala and DCGL are being inducted accordingly._x000D_
-•	All departments should be doing tool box talk before starting work each and every day in order to maintain safety procedures. _x000D_
+    <t>["a)\tLack of transport", "\u2022\tTransportation of herbicides to various fields has been a challenge for herbicide team therefore push bikes must issued to this team.", "b)\tPPE for Workers", "\u2022\tPPE need to be issued to all employees for them to be safe at working places.", "\u2022\tCane smokes for cane cutters are worn out therefore purchasing of these cane smokes is urgently needed.", "\u2022\tPurchase of mesh wire goggles is also needed as most of those issued already are unconditional.", "\u2022\tHerbicide team needs to be issued at least 2 PPE per person and per season.", "\u2022\tHerbicide team are working with worn out attire hence issuing of PPE is urgently needed for them to be safe.", "\u2022\tPurchasing of safety corns is needed for identifying the resting places at cane cutting front as advised by Illovo.", "c)\tLack of First Aid/aiders", "\u2022\tFirst aiders don\u2019t have full first aid equipment e.g. first aid boxes or bags etc.", "\u2022\tAt general agriculture there is nobody who has knowledge in first aid hence training is needed for first aiders.", "d)\tToilets and Bath rooms", "\u2022\tBath rooms at Kayeleka cane cutting compound needs to be cleaned by responsible personnel.", "\u2022\tToilets behind DGCL Hall need to be demolished as both are full and unconditional.", "e)\tHousing", "\u2022\tMost of houses in both Kayeleka and Chawala compounds need maintenance.", "\u2022\tFor easy identification, all Chawala and Kayeleka houses need to be numbered.", "\u2022\tAll houses need painting (Lime).", "f)\tConstruction of bathrooms\u2019/change rooms", "\u2022\tThe process of constructing the bathrooms at field office is still in the progress and the most problem is the pressure of water which is very low compared to the pressure which is needed to be used therefore pipe line from main tanks to field office should looked into."]</t>
+  </si>
+  <si>
+    <t>["No proper housing", "Poor sanitation in the compound"]</t>
+  </si>
+  <si>
+    <t>["Bad housing"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	All employees of both Chawala and DCGL are being inducted accordingly._x005F_x000D_
+•	All departments should be doing tool box talk before starting work each and every day in order to maintain safety procedures. _x005F_x000D_
 </t>
   </si>
   <si>
-    <t xml:space="preserve">•	At harvesting (Chawala) only 3 minor injuries were recorded during the month._x000D_
-•	All injuries were due to a cut by cane knives._x000D_
-•	At general agriculture 4 injuries were recorded during the month due to sugarcane leaves._x000D_
-•	To avoid such injuries workers should be advising to apply four steps to safety and four currencies while on duty rather than just memorizing them._x000D_
-•	Behavior change on the matter of safety should be taken into consideration._x000D_
-_x000D_
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
+    <t>Node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	At harvesting (Chawala) only 3 minor injuries were recorded during the month._x005F_x000D_
+•	All injuries were due to a cut by cane knives._x005F_x000D_
+•	At general agriculture 4 injuries were recorded during the month due to sugarcane leaves._x005F_x000D_
+•	To avoid such injuries workers should be advising to apply four steps to safety and four currencies while on duty rather than just memorizing them._x005F_x000D_
+•	Behavior change on the matter of safety should be taken into consideration._x005F_x000D_
+_x005F_x000D_
 </t>
   </si>
   <si>
-    <t xml:space="preserve">•	Most of the houses don’t have conditional doors hence snakes are entering in the houses putting people’s lives at risk. _x000D_
-•	The charging of phone batteries using boosters is now at large in all the departments (HR, Agriculture and Finance Department) which is very dangerous and can cause unexpected fire accidents._x000D_
-•	At main office the workshop roof/canopy need renovation in order to safe guard those who are using it._x000D_
+    <t>11 injuries from cane cutting</t>
+  </si>
+  <si>
+    <t>Cut on the finger by glass 16, twisted leg 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•	Most of the houses don’t have conditional doors hence snakes are entering in the houses putting people’s lives at risk. _x005F_x000D_
+•	The charging of phone batteries using boosters is now at large in all the departments (HR, Agriculture and Finance Department) which is very dangerous and can cause unexpected fire accidents._x005F_x000D_
+•	At main office the workshop roof/canopy need renovation in order to safe guard those who are using it._x005F_x000D_
 </t>
   </si>
   <si>
+    <t>Sharp knives, sugarcane leaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wet working conditions </t>
+  </si>
+  <si>
     <t>•	Tractor trailers should be maintained to avoid injuries to those who are using it.</t>
   </si>
   <si>
+    <t>Bad seat on BU894_x005F_x000D_
+Trailers need maintenance</t>
+  </si>
+  <si>
+    <t>BU892 seat in bad state</t>
+  </si>
+  <si>
     <t xml:space="preserve">•	No one has died. </t>
   </si>
   <si>
-    <t>2025-12-17 09:53:48</t>
+    <t>No report</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2025-12-18 18:45:29</t>
+  </si>
+  <si>
+    <t>2025-12-18 18:48:03</t>
+  </si>
+  <si>
+    <t>2025-12-18 19:00:28</t>
+  </si>
+  <si>
+    <t>2025-12-18 19:42:18</t>
+  </si>
+  <si>
+    <t>2025-12-19 05:53:38</t>
+  </si>
+  <si>
+    <t>•	SHEQ team should be promoted to permanent employees due to nature of their job.</t>
+  </si>
+  <si>
+    <t>Need a permanet team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make this office staff permanent employees for continuity </t>
   </si>
 </sst>
 </file>
@@ -466,10 +563,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,55 +615,276 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" t="s">
+        <v>54</v>
+      </c>
+      <c r="R4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="N2">
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6">
         <v>1</v>
       </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" t="s">
-        <v>27</v>
+      <c r="O6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_safety_reports.xlsx
+++ b/data/monthly_safety_reports.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -73,16 +73,7 @@
     <t>5ccca35e88224b449a254cc79730a356</t>
   </si>
   <si>
-    <t>5460b636e23b46aab9fc27f9866a764c</t>
-  </si>
-  <si>
-    <t>53de2581eef04cacbf64a6859d84dcbe</t>
-  </si>
-  <si>
-    <t>517955eaf98640af92085cba34d4f8f8</t>
-  </si>
-  <si>
-    <t>73a22ce99bd7486798c6aec72250b8d5</t>
+    <t>43f4d8562eed491d9d7b759891e73e86</t>
   </si>
   <si>
     <t>MSR-2025-12-001</t>
@@ -91,9 +82,6 @@
     <t>2025-05</t>
   </si>
   <si>
-    <t>2024-11</t>
-  </si>
-  <si>
     <t>2025-01</t>
   </si>
   <si>
@@ -112,19 +100,13 @@
     <t>{"Human Resources": {"permanent": 0, "seasonal": 0, "casual": 0}, "General Agriculture": {"permanent": 1, "seasonal": 4, "casual": 0}, "Accounts Department": {"permanent": 0, "seasonal": 0, "casual": 0}}</t>
   </si>
   <si>
-    <t>{"Human Resources": {"permanent": 1, "seasonal": 0, "casual": 0}, "General Agriculture": {"permanent": 0, "seasonal": 3, "casual": 1}, "Accounts Department": {"permanent": 0, "seasonal": 0, "casual": 0}}</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
     <t>["a)\tLack of transport", "\u2022\tTransportation of herbicides to various fields has been a challenge for herbicide team therefore push bikes must issued to this team.", "b)\tPPE for Workers", "\u2022\tPPE need to be issued to all employees for them to be safe at working places.", "\u2022\tCane smokes for cane cutters are worn out therefore purchasing of these cane smokes is urgently needed.", "\u2022\tPurchase of mesh wire goggles is also needed as most of those issued already are unconditional.", "\u2022\tHerbicide team needs to be issued at least 2 PPE per person and per season.", "\u2022\tHerbicide team are working with worn out attire hence issuing of PPE is urgently needed for them to be safe.", "\u2022\tPurchasing of safety corns is needed for identifying the resting places at cane cutting front as advised by Illovo.", "c)\tLack of First Aid/aiders", "\u2022\tFirst aiders don\u2019t have full first aid equipment e.g. first aid boxes or bags etc.", "\u2022\tAt general agriculture there is nobody who has knowledge in first aid hence training is needed for first aiders.", "d)\tToilets and Bath rooms", "\u2022\tBath rooms at Kayeleka cane cutting compound needs to be cleaned by responsible personnel.", "\u2022\tToilets behind DGCL Hall need to be demolished as both are full and unconditional.", "e)\tHousing", "\u2022\tMost of houses in both Kayeleka and Chawala compounds need maintenance.", "\u2022\tFor easy identification, all Chawala and Kayeleka houses need to be numbered.", "\u2022\tAll houses need painting (Lime).", "f)\tConstruction of bathrooms\u2019/change rooms", "\u2022\tThe process of constructing the bathrooms at field office is still in the progress and the most problem is the pressure of water which is very low compared to the pressure which is needed to be used therefore pipe line from main tanks to field office should looked into."]</t>
   </si>
   <si>
-    <t>["No proper housing", "Poor sanitation in the compound"]</t>
-  </si>
-  <si>
-    <t>["Bad housing"]</t>
+    <t>["1 2  1 2"]</t>
   </si>
   <si>
     <t xml:space="preserve">•	All employees of both Chawala and DCGL are being inducted accordingly._x005F_x000D_
@@ -132,10 +114,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Done </t>
-  </si>
-  <si>
-    <t>Node</t>
+    <t>Kuyesa nawo</t>
   </si>
   <si>
     <t xml:space="preserve">•	At harvesting (Chawala) only 3 minor injuries were recorded during the month._x005F_x000D_
@@ -147,10 +126,7 @@
 </t>
   </si>
   <si>
-    <t>11 injuries from cane cutting</t>
-  </si>
-  <si>
-    <t>Cut on the finger by glass 16, twisted leg 4</t>
+    <t>Ndithu kuyesa cahabe</t>
   </si>
   <si>
     <t xml:space="preserve">•	Most of the houses don’t have conditional doors hence snakes are entering in the houses putting people’s lives at risk. _x005F_x000D_
@@ -159,26 +135,19 @@
 </t>
   </si>
   <si>
-    <t>Sharp knives, sugarcane leaf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wet working conditions </t>
+    <t xml:space="preserve">Testing </t>
   </si>
   <si>
     <t>•	Tractor trailers should be maintained to avoid injuries to those who are using it.</t>
   </si>
   <si>
-    <t>Bad seat on BU894_x005F_x000D_
-Trailers need maintenance</t>
-  </si>
-  <si>
-    <t>BU892 seat in bad state</t>
+    <t>Kuyesa</t>
   </si>
   <si>
     <t xml:space="preserve">•	No one has died. </t>
   </si>
   <si>
-    <t>No report</t>
+    <t>kuyesa nawo</t>
   </si>
   <si>
     <t>1</t>
@@ -187,25 +156,13 @@
     <t>2025-12-18 18:45:29</t>
   </si>
   <si>
-    <t>2025-12-18 18:48:03</t>
-  </si>
-  <si>
-    <t>2025-12-18 19:00:28</t>
-  </si>
-  <si>
-    <t>2025-12-18 19:42:18</t>
-  </si>
-  <si>
-    <t>2025-12-19 05:53:38</t>
+    <t>2025-12-21 06:56:21</t>
   </si>
   <si>
     <t>•	SHEQ team should be promoted to permanent employees due to nature of their job.</t>
   </si>
   <si>
-    <t>Need a permanet team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Make this office staff permanent employees for continuity </t>
+    <t>Tikuyesa</t>
   </si>
 </sst>
 </file>
@@ -563,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -627,52 +584,52 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>33</v>
       </c>
-      <c r="H2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" t="s">
-        <v>46</v>
-      </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -680,211 +637,52 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
         <v>34</v>
       </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
         <v>40</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" t="s">
-        <v>53</v>
-      </c>
       <c r="P3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P4" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P5" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" t="s">
-        <v>56</v>
-      </c>
-      <c r="R6" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
